--- a/data/trans_orig/ProbViv_temp-Clase-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_temp-Clase-trans_orig.xlsx
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26215</t>
+          <t>26388</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43954</t>
+          <t>43942</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34268</t>
+          <t>33877</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55468</t>
+          <t>55754</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65620</t>
+          <t>66217</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93556</t>
+          <t>94595</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60508</t>
+          <t>60520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78247</t>
+          <t>78074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80497</t>
+          <t>80211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101697</t>
+          <t>102088</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146870</t>
+          <t>145831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174806</t>
+          <t>174209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,46%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25099</t>
+          <t>25548</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40960</t>
+          <t>41073</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25822</t>
+          <t>25021</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42081</t>
+          <t>41680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55368</t>
+          <t>56086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>78496</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53721</t>
+          <t>53608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69582</t>
+          <t>69133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53492</t>
+          <t>53893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69751</t>
+          <t>70552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111610</t>
+          <t>111758</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134886</t>
+          <t>134168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,52%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28307</t>
+          <t>27922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18705</t>
+          <t>18772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32795</t>
+          <t>33771</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37869</t>
+          <t>37761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57519</t>
+          <t>57746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23554</t>
+          <t>23939</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>35951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31058</t>
+          <t>30082</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45148</t>
+          <t>45081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58195</t>
+          <t>57968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77845</t>
+          <t>77953</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74283</t>
+          <t>74080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141274</t>
+          <t>140054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60107</t>
+          <t>61264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86044</t>
+          <t>87818</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145247</t>
+          <t>143619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>230353</t>
+          <t>224587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>51,5%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76552</t>
+          <t>77772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143543</t>
+          <t>143746</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>132228</t>
+          <t>130454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>158165</t>
+          <t>157008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205744</t>
+          <t>211510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290850</t>
+          <t>292478</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50291</t>
+          <t>50428</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69380</t>
+          <t>68646</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55540</t>
+          <t>54564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83437</t>
+          <t>84862</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109724</t>
+          <t>108098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145137</t>
+          <t>145538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50048</t>
+          <t>50782</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69137</t>
+          <t>69000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79180</t>
+          <t>77755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>108053</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>136507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>172321</t>
+          <t>173947</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,67%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30667</t>
+          <t>30790</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>45557</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>29473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44580</t>
+          <t>45105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64366</t>
+          <t>64256</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>85032</t>
+          <t>84873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>38105</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27423</t>
+          <t>26898</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42983</t>
+          <t>42530</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55866</t>
+          <t>56025</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76532</t>
+          <t>76642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>255805</t>
+          <t>256028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>333111</t>
+          <t>332084</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>257752</t>
+          <t>259377</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>308203</t>
+          <t>309683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>528514</t>
+          <t>533047</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>628142</t>
+          <t>627976</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>324042</t>
+          <t>325069</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>401348</t>
+          <t>401125</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>440079</t>
+          <t>438599</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>490530</t>
+          <t>488905</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>777293</t>
+          <t>777459</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>876921</t>
+          <t>872388</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProbViv_temp-Clase-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_temp-Clase-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>71637</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>80455</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>71637</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>71637</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>71637</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>71637</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>80455</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>80455</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>80455</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>71637</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>71637</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>71637</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>67485</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>68687</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>67485</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67485</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67485</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67485</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>68687</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>68687</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>68687</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>67485</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>67485</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>67485</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>83944</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>58245</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>83944</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>83944</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>83944</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>83944</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>58245</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>58245</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>58245</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>83944</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>83944</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>83944</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1865,47 +1865,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>148562</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>151296</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>148562</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148562</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148562</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148562</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151296</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151296</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151296</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148562</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148562</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148562</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,47 +2208,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>84530</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>69123</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>84530</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>84530</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>84530</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>84530</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>69123</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>69123</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>69123</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>84530</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>84530</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>84530</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2551,47 +2551,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2664,57 +2664,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2894,47 +2894,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>745</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>502675</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3007,57 +3007,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>745</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>502675</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>502675</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>502675</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3190,7 +3190,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3471,47 +3471,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>73410</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>61221</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>73410</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3584,57 +3584,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>73410</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>73410</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>73410</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>61221</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>61221</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>61221</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>73410</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>73410</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>73410</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3814,47 +3814,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>68526</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>65379</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>68526</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3927,57 +3927,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>68526</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>68526</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>68526</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>65379</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>65379</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>65379</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>68526</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>68526</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>68526</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4157,47 +4157,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67964</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66523</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67964</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4270,57 +4270,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>67964</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>67964</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>67964</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66523</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66523</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66523</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>67964</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>67964</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>67964</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4500,47 +4500,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>161364</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>136480</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>161364</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4613,57 +4613,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>161364</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>161364</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>161364</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>136480</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>136480</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>136480</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>161364</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>161364</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>161364</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4843,47 +4843,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>92008</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>93451</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>92008</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4956,57 +4956,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>92008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>92008</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>92008</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>93451</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>93451</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>93451</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>92008</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>92008</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>92008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5186,47 +5186,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5299,57 +5299,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5529,47 +5529,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>537310</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>537310</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -5642,57 +5642,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>537310</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>537310</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>537310</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>537310</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>537310</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>537310</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5825,7 +5825,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6106,47 +6106,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>78254</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>64831</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>78254</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6219,57 +6219,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>78254</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>78254</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>78254</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>64831</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>64831</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>64831</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>78254</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>78254</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>78254</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6449,47 +6449,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>93067</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>82311</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>93067</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6562,57 +6562,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>93067</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>93067</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>93067</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>82311</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>82311</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>82311</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>93067</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>93067</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>93067</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6792,47 +6792,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>61011</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>49224</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>61011</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6905,57 +6905,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61011</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>61011</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>61011</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>49224</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>49224</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>49224</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>61011</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>61011</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>61011</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7135,47 +7135,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>170883</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>165797</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>170883</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7248,57 +7248,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170883</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170883</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170883</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165797</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165797</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165797</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170883</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170883</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170883</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7478,47 +7478,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>99153</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>101579</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>99153</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -7591,57 +7591,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>99153</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>99153</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>99153</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>101579</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>101579</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>101579</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>99153</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>99153</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>99153</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7821,47 +7821,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>60334</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7934,57 +7934,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>60334</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>60334</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>60334</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8164,47 +8164,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>570192</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>788</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>524076</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>570192</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -8277,57 +8277,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>570192</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>570192</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>570192</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>788</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>524076</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>524076</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>524076</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>570192</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>570192</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>570192</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8460,7 +8460,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8628,72 +8628,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41291</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32218</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51059</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>41,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>34369</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26388</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43942</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32,9%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44554</t>
+          <t>32474</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55754</t>
+          <t>40500</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>78923</t>
+          <t>73766</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66217</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94595</t>
+          <t>85270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -8741,72 +8741,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80326</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>70558</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>89399</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>58,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>70093</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>60520</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>78074</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>67,1%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57,93%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91411</t>
+          <t>70453</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80211</t>
+          <t>62427</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102088</t>
+          <t>78395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>161503</t>
+          <t>150779</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145831</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174209</t>
+          <t>163823</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -8854,57 +8854,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121617</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121617</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121617</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135965</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135965</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135965</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>240426</t>
+          <t>224545</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>240426</t>
+          <t>224545</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>240426</t>
+          <t>224545</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8971,72 +8971,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33593</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24575</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41553</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>45,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33206</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25548</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>41073</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>35,07%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>43,38%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33929</t>
+          <t>35098</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25021</t>
+          <t>26510</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41680</t>
+          <t>43143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>67135</t>
+          <t>68690</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56086</t>
+          <t>57690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78496</t>
+          <t>79145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -9084,72 +9084,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>57805</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49845</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>66823</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>63,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>54,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>61475</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>53608</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>69133</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>64,93%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>56,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61644</t>
+          <t>61448</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53893</t>
+          <t>53403</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70552</t>
+          <t>70036</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>123119</t>
+          <t>119254</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111758</t>
+          <t>108799</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134168</t>
+          <t>130254</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -9197,57 +9197,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>22364</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27922</t>
+          <t>29575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25321</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18772</t>
+          <t>16774</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33771</t>
+          <t>29102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47105</t>
+          <t>45133</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37761</t>
+          <t>36293</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57746</t>
+          <t>55174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,97%</t>
         </is>
       </c>
     </row>
@@ -9427,72 +9427,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34577</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27366</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>41096</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>60,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>48,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30077</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23939</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35951</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>58,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>46,16%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>69,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30082</t>
+          <t>24380</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45081</t>
+          <t>36708</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>68609</t>
+          <t>65290</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57968</t>
+          <t>55249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77953</t>
+          <t>74130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,13%</t>
         </is>
       </c>
     </row>
@@ -9540,57 +9540,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9657,72 +9657,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68525</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>57068</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>82381</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,79%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>96456</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>74080</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>140054</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>44,28%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34,01%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>64,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>63843</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61264</t>
+          <t>53330</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87818</t>
+          <t>74318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>169457</t>
+          <t>132369</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143619</t>
+          <t>117409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>224587</t>
+          <t>149330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -9770,72 +9770,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>133419</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>119563</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>144876</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,07%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>59,21%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>71,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>121370</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>77772</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>143746</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>55,72%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65,99%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>145271</t>
+          <t>114740</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130454</t>
+          <t>104265</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157008</t>
+          <t>125253</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>266640</t>
+          <t>248159</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211510</t>
+          <t>231198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292478</t>
+          <t>263119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
@@ -9883,57 +9883,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10000,72 +10000,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>66360</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>51379</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>78028</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>44,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,66%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>52,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>59265</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>50428</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>68646</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>49,62%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>57,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>70884</t>
+          <t>58808</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54564</t>
+          <t>50320</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84862</t>
+          <t>68010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>130149</t>
+          <t>125168</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108098</t>
+          <t>108402</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145538</t>
+          <t>139774</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -10113,72 +10113,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>81883</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>70215</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>96864</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>55,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>47,36%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,34%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>60163</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>50782</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>69000</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>50,38%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>42,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>57,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91733</t>
+          <t>59923</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77755</t>
+          <t>50721</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108053</t>
+          <t>68411</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>151896</t>
+          <t>141806</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136507</t>
+          <t>127200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173947</t>
+          <t>158572</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>59,4%</t>
         </is>
       </c>
     </row>
@@ -10226,57 +10226,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10343,72 +10343,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>35857</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>28136</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>42590</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>52,51%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>41,2%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>62,37%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>37932</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>30790</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>45557</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>55,06%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>44,69%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>66,12%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>36810</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29473</t>
+          <t>30257</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45105</t>
+          <t>46079</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>74742</t>
+          <t>74390</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64256</t>
+          <t>63670</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84873</t>
+          <t>85724</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>61,83%</t>
         </is>
       </c>
     </row>
@@ -10456,72 +10456,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32430</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>25697</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>40151</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>47,49%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>37,63%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>58,8%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>30963</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>23338</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>38105</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>44,94%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>33,88%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>55,31%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>35193</t>
+          <t>31824</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26898</t>
+          <t>24277</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42530</t>
+          <t>40099</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>66156</t>
+          <t>64254</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56025</t>
+          <t>52920</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76642</t>
+          <t>74974</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -10569,57 +10569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10686,72 +10686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>267990</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>243646</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>290736</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>38,93%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>35,39%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>42,23%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>363</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>283012</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>256028</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>332084</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>38,96%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>50,53%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>284499</t>
+          <t>251525</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>259377</t>
+          <t>231628</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>309683</t>
+          <t>274007</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>567510</t>
+          <t>519515</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>533047</t>
+          <t>487057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>627976</t>
+          <t>553181</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -10799,72 +10799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>420440</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>397694</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>444784</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>61,07%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>57,77%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>64,61%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>566</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>374141</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>325069</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>401125</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>49,47%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>61,04%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>463783</t>
+          <t>369102</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>438599</t>
+          <t>346620</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>488905</t>
+          <t>388999</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>837925</t>
+          <t>789542</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>777459</t>
+          <t>755876</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>872388</t>
+          <t>822000</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,79%</t>
         </is>
       </c>
     </row>
@@ -10912,57 +10912,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>688430</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>688430</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>688430</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>748282</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>748282</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>748282</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1405435</t>
+          <t>1309057</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1405435</t>
+          <t>1309057</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1405435</t>
+          <t>1309057</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
